--- a/artfynd/A 38647-2019 artfynd.xlsx
+++ b/artfynd/A 38647-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38647-2019 artfynd.xlsx
+++ b/artfynd/A 38647-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57703667</v>
+        <v>57703655</v>
       </c>
       <c r="B4" t="n">
-        <v>95511</v>
+        <v>103250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,21 +933,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>221725</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>754710.3644311076</v>
+        <v>754679.3706236526</v>
       </c>
       <c r="R4" t="n">
-        <v>7464429.391242558</v>
+        <v>7464438.932406883</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57703655</v>
+        <v>91822547</v>
       </c>
       <c r="B5" t="n">
-        <v>103250</v>
+        <v>86210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,41 +1050,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>4412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2,6 km NV om Myrheden, Lu lm</t>
+          <t>Nautanen-Liikavaara, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>754679.3706236526</v>
+        <v>754702.0676032358</v>
       </c>
       <c r="R5" t="n">
-        <v>7464438.932406883</v>
+        <v>7464220.937678206</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-07-08</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-07-08</t>
+          <t>2020-09-02</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1134,35 +1134,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Sumpblandskog i ravin</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lars Fröberg</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lars Fröberg, Lennart Persson, Rolf Enander, Elin Götmark, Annelie Jörgensen, Nannie Persson, Ola Löfgren, Vivi Eriksson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
+          <t>per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91822547</v>
+        <v>57703664</v>
       </c>
       <c r="B6" t="n">
-        <v>86210</v>
+        <v>96222</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,41 +1162,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>233</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Oakes</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nautanen-Liikavaara, Lu lm</t>
+          <t>2,6 km NV om Myrheden, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>754702.0676032358</v>
+        <v>754685.2878850732</v>
       </c>
       <c r="R6" t="n">
-        <v>7464220.937678206</v>
+        <v>7464430.127559965</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,7 +1231,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2015-07-08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1239,7 +1241,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2015-07-08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1247,6 +1249,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lokal känd av Vivi Eriksson</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1255,23 +1262,32 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Sumpblandskog i ravin</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lars Fröberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Lars Fröberg, Lennart Persson, Rolf Enander, Elin Götmark, Annelie Jörgensen, Nannie Persson, Ola Löfgren, Vivi Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Florainventering av vita fläckar i Lappland</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>57703664</v>
+        <v>57703673</v>
       </c>
       <c r="B7" t="n">
         <v>96222</v>
@@ -1322,10 +1338,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>754685.2878850732</v>
+        <v>754677.3049717732</v>
       </c>
       <c r="R7" t="n">
-        <v>7464430.127559965</v>
+        <v>7464436.00354653</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1408,7 +1424,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>57703673</v>
+        <v>57703647</v>
       </c>
       <c r="B8" t="n">
         <v>96222</v>
@@ -1441,28 +1457,17 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>2,6 km NV om Myrheden, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>754677.3049717732</v>
+        <v>754679.3706236526</v>
       </c>
       <c r="R8" t="n">
-        <v>7464436.00354653</v>
+        <v>7464438.932406883</v>
       </c>
       <c r="S8" t="n">
         <v>100</v>
@@ -1545,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57703647</v>
+        <v>57703666</v>
       </c>
       <c r="B9" t="n">
         <v>96222</v>
@@ -1578,17 +1583,28 @@
           <t>(L.) Oakes</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>2,6 km NV om Myrheden, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>754679.3706236526</v>
+        <v>754710.3644311076</v>
       </c>
       <c r="R9" t="n">
-        <v>7464438.932406883</v>
+        <v>7464429.391242558</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -1664,143 +1680,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr">
-        <is>
-          <t>Florainventering av vita fläckar i Lappland</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>57703666</v>
-      </c>
-      <c r="B10" t="n">
-        <v>96222</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>233</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Norna</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Calypso bulbosa</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2,6 km NV om Myrheden, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>754710.3644311076</v>
-      </c>
-      <c r="R10" t="n">
-        <v>7464429.391242558</v>
-      </c>
-      <c r="S10" t="n">
-        <v>100</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2015-07-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2015-07-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Lokal känd av Vivi Eriksson</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Sumpblandskog i ravin</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Lars Fröberg</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Lars Fröberg, Lennart Persson, Rolf Enander, Elin Götmark, Annelie Jörgensen, Nannie Persson, Ola Löfgren, Vivi Eriksson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
         <is>
           <t>Florainventering av vita fläckar i Lappland</t>
         </is>
